--- a/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8D44C45-F3EB-874C-91C1-BFB33FD2E51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFE9BFC-935C-F64A-99E2-9EBC4C33A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5140" yWindow="1220" windowWidth="27900" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
+    <workbookView xWindow="1500" yWindow="1220" windowWidth="27900" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
   <si>
     <t>Document ID</t>
   </si>
@@ -61,9 +61,6 @@
     <t>CF_M08_M01</t>
   </si>
   <si>
-    <t>CF_M09_AU03</t>
-  </si>
-  <si>
     <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>CF_M08_M04</t>
   </si>
   <si>
-    <t>CF_M09_AU22</t>
-  </si>
-  <si>
     <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
   </si>
   <si>
@@ -91,9 +85,6 @@
     <t>CF_M08_M06</t>
   </si>
   <si>
-    <t>CF_M09_AU05</t>
-  </si>
-  <si>
     <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
   </si>
   <si>
@@ -118,9 +109,6 @@
     <t>CF_M08_M10</t>
   </si>
   <si>
-    <t>CF_M09_AU06</t>
-  </si>
-  <si>
     <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
   </si>
   <si>
@@ -139,9 +127,6 @@
     <t>CF_M08_M14</t>
   </si>
   <si>
-    <t>CF_M09_AU09</t>
-  </si>
-  <si>
     <t>It is designed to simplify access and database management</t>
   </si>
   <si>
@@ -155,6 +140,69 @@
   </si>
   <si>
     <t>facilitating development and debugging.</t>
+  </si>
+  <si>
+    <t>CF_M08_AU03</t>
+  </si>
+  <si>
+    <t>CF_M08_AU22</t>
+  </si>
+  <si>
+    <t>CF_M08_AU05</t>
+  </si>
+  <si>
+    <t>CF_M08_AU06</t>
+  </si>
+  <si>
+    <t>CF_M08_AU09</t>
+  </si>
+  <si>
+    <t>CF_M08_C01</t>
+  </si>
+  <si>
+    <t>CF_M08_C02</t>
+  </si>
+  <si>
+    <t>CF_M08_C03</t>
+  </si>
+  <si>
+    <t>CF_M08_C04</t>
+  </si>
+  <si>
+    <t>CF_M08_C05</t>
+  </si>
+  <si>
+    <t>CF_M08_C06</t>
+  </si>
+  <si>
+    <t>CF_M08_C07</t>
+  </si>
+  <si>
+    <t>CF_M08_C08</t>
+  </si>
+  <si>
+    <t>CF_M08_C09</t>
+  </si>
+  <si>
+    <t>CF_M08_C10</t>
+  </si>
+  <si>
+    <t>CF_M08_C11</t>
+  </si>
+  <si>
+    <t>CF_M08_C12</t>
+  </si>
+  <si>
+    <t>CF_M08_C13</t>
+  </si>
+  <si>
+    <t>CF_M08_C14</t>
+  </si>
+  <si>
+    <t>CF_M08_C15</t>
+  </si>
+  <si>
+    <t>CF_M08_C16</t>
   </si>
 </sst>
 </file>
@@ -630,13 +678,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>9</v>
       </c>
       <c r="F2" s="8">
         <v>43</v>
@@ -647,16 +695,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>9</v>
       </c>
       <c r="F3" s="8">
         <v>43</v>
@@ -667,16 +715,16 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>12</v>
       </c>
       <c r="F4" s="9">
         <v>43</v>
@@ -687,16 +735,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>15</v>
       </c>
       <c r="F5" s="9">
         <v>43</v>
@@ -707,16 +755,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F6" s="9">
         <v>43</v>
@@ -727,16 +775,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F7" s="9">
         <v>45</v>
@@ -747,16 +795,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>18</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="F8" s="9">
         <v>45</v>
@@ -767,16 +815,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F9" s="9">
         <v>45</v>
@@ -787,16 +835,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F10" s="9">
         <v>45</v>
@@ -807,16 +855,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F11" s="9">
         <v>47</v>
@@ -827,16 +875,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F12" s="9">
         <v>47</v>
@@ -847,16 +895,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="F13" s="9">
         <v>47</v>
@@ -867,16 +915,16 @@
         <v>6</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>31</v>
       </c>
       <c r="F14" s="9">
         <v>47</v>
@@ -887,16 +935,16 @@
         <v>6</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F15" s="9">
         <v>50</v>
@@ -907,16 +955,16 @@
         <v>6</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F16" s="9">
         <v>50</v>
@@ -927,16 +975,16 @@
         <v>6</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="F17" s="9">
         <v>50</v>

--- a/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AFE9BFC-935C-F64A-99E2-9EBC4C33A4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFEB066-799C-0F44-BF9D-FF13C805CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1220" windowWidth="27900" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
+    <workbookView xWindow="1500" yWindow="1200" windowWidth="27900" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
   <si>
     <t>Document ID</t>
   </si>
@@ -58,90 +58,30 @@
     <t>CF_M08</t>
   </si>
   <si>
-    <t>CF_M08_M01</t>
-  </si>
-  <si>
     <t>Load Balancer: Distributes traffic between multiple instances of a service, improving the availability and responsiveness of the application</t>
   </si>
   <si>
-    <t>CF_M08_M02</t>
-  </si>
-  <si>
-    <t>CF_M08_M03</t>
-  </si>
-  <si>
-    <t>ensure that all communications are carried out securely</t>
-  </si>
-  <si>
-    <t>CF_M08_M04</t>
-  </si>
-  <si>
     <t>HTTPS encrypts the data transmitted between the clients and the server, protecting the integrity and confidentiality of the information.</t>
   </si>
   <si>
-    <t>CF_M08_M05</t>
-  </si>
-  <si>
-    <t>CF_M08_M06</t>
-  </si>
-  <si>
     <t>This facilitates the creation of paths by simply adding files and folders inside the src directory.</t>
   </si>
   <si>
-    <t>CF_M08_M07</t>
-  </si>
-  <si>
     <t>Next.js supports several styling methods, including CSS, Tailwind CSS and CSS-in-JS modules, offering flexibility in style management</t>
   </si>
   <si>
-    <t>CF_M08_M08</t>
-  </si>
-  <si>
     <t>It includes automatic optimizations for images, fonts and scripts, improving the performance of the application.</t>
   </si>
   <si>
-    <t>CF_M08_M09</t>
-  </si>
-  <si>
-    <t>allowing a simpler and more direct integration of the server's logic in the application.</t>
-  </si>
-  <si>
-    <t>CF_M08_M10</t>
-  </si>
-  <si>
     <t>React is an open source JavaScript library designed to build user interfaces (UI) efficiently and flexibly</t>
   </si>
   <si>
-    <t>CF_M08_M11</t>
-  </si>
-  <si>
-    <t>CF_M08_M12</t>
-  </si>
-  <si>
     <t>React allows developers to create dynamic and fast web applications by facilitating the creation of reusable and modular components</t>
   </si>
   <si>
-    <t>CF_M08_M13</t>
-  </si>
-  <si>
-    <t>CF_M08_M14</t>
-  </si>
-  <si>
     <t>It is designed to simplify access and database management</t>
   </si>
   <si>
-    <t>CF_M08_M15</t>
-  </si>
-  <si>
-    <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server</t>
-  </si>
-  <si>
-    <t>CF_M08_M16</t>
-  </si>
-  <si>
-    <t>facilitating development and debugging.</t>
-  </si>
-  <si>
     <t>CF_M08_AU03</t>
   </si>
   <si>
@@ -157,21 +97,9 @@
     <t>CF_M08_AU09</t>
   </si>
   <si>
-    <t>CF_M08_C01</t>
-  </si>
-  <si>
-    <t>CF_M08_C02</t>
-  </si>
-  <si>
     <t>CF_M08_C03</t>
   </si>
   <si>
-    <t>CF_M08_C04</t>
-  </si>
-  <si>
-    <t>CF_M08_C05</t>
-  </si>
-  <si>
     <t>CF_M08_C06</t>
   </si>
   <si>
@@ -184,25 +112,74 @@
     <t>CF_M08_C09</t>
   </si>
   <si>
-    <t>CF_M08_C10</t>
-  </si>
-  <si>
-    <t>CF_M08_C11</t>
-  </si>
-  <si>
-    <t>CF_M08_C12</t>
-  </si>
-  <si>
-    <t>CF_M08_C13</t>
-  </si>
-  <si>
     <t>CF_M08_C14</t>
   </si>
   <si>
-    <t>CF_M08_C15</t>
-  </si>
-  <si>
     <t>CF_M08_C16</t>
+  </si>
+  <si>
+    <t>CF_M08_C01, CF_M08_C02</t>
+  </si>
+  <si>
+    <t>CF_M08_C04, CF_M08_C05</t>
+  </si>
+  <si>
+    <t>CF_M08_C10, CF_M08_C11</t>
+  </si>
+  <si>
+    <t>CF_M08_C12, CF_M08_C13</t>
+  </si>
+  <si>
+    <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
+  </si>
+  <si>
+    <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+  </si>
+  <si>
+    <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+  </si>
+  <si>
+    <t>CF_M08_C15,</t>
+  </si>
+  <si>
+    <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
+directing this traffic to port 443 (HTTPS) to ensure that all communications are carried out safely.</t>
+  </si>
+  <si>
+    <t>CF_M08_AD01</t>
+  </si>
+  <si>
+    <t>CF_M08_AD02</t>
+  </si>
+  <si>
+    <t>CF_M08_AD03</t>
+  </si>
+  <si>
+    <t>CF_M08_AD04</t>
+  </si>
+  <si>
+    <t>CF_M08_AD05</t>
+  </si>
+  <si>
+    <t>CF_M08_AD06</t>
+  </si>
+  <si>
+    <t>CF_M08_AD07</t>
+  </si>
+  <si>
+    <t>CF_M08_AD08</t>
+  </si>
+  <si>
+    <t>CF_M08_AD09</t>
+  </si>
+  <si>
+    <t>CF_M08_AD10</t>
+  </si>
+  <si>
+    <t>CF_M08_AD11</t>
+  </si>
+  <si>
+    <t>CF_M08_AD12</t>
   </si>
 </sst>
 </file>
@@ -641,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D616AB-2B88-2A42-A2F9-40D380514760}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -675,16 +652,16 @@
         <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="F2" s="8">
         <v>43</v>
@@ -694,37 +671,37 @@
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>9</v>
+      <c r="B3" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="9">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="F3" s="8">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="F4" s="9">
         <v>43</v>
@@ -735,19 +712,19 @@
         <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F5" s="9">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="29" x14ac:dyDescent="0.2">
@@ -755,19 +732,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6" s="9">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.2">
@@ -775,39 +752,39 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F7" s="9">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="71" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="D8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="9">
         <v>46</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="9">
-        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.2">
@@ -815,19 +792,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="9">
         <v>47</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="9">
-        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.2">
@@ -835,39 +812,39 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F10" s="9">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="29" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="C11" s="6" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F11" s="9">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="29" x14ac:dyDescent="0.2">
@@ -875,118 +852,38 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="9">
         <v>50</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="9">
+    </row>
+    <row r="13" spans="1:6" ht="43" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="29" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>51</v>
-      </c>
       <c r="E13" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F13" s="9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="29" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="9">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F15" s="9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="29" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="9">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="9">
         <v>50</v>
       </c>
     </row>

--- a/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFEB066-799C-0F44-BF9D-FF13C805CBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4030650F-4F0D-7148-A85D-3EC4E5D41168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1200" windowWidth="27900" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
+    <workbookView xWindow="17260" yWindow="940" windowWidth="18620" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -97,39 +97,6 @@
     <t>CF_M08_AU09</t>
   </si>
   <si>
-    <t>CF_M08_C03</t>
-  </si>
-  <si>
-    <t>CF_M08_C06</t>
-  </si>
-  <si>
-    <t>CF_M08_C07</t>
-  </si>
-  <si>
-    <t>CF_M08_C08</t>
-  </si>
-  <si>
-    <t>CF_M08_C09</t>
-  </si>
-  <si>
-    <t>CF_M08_C14</t>
-  </si>
-  <si>
-    <t>CF_M08_C16</t>
-  </si>
-  <si>
-    <t>CF_M08_C01, CF_M08_C02</t>
-  </si>
-  <si>
-    <t>CF_M08_C04, CF_M08_C05</t>
-  </si>
-  <si>
-    <t>CF_M08_C10, CF_M08_C11</t>
-  </si>
-  <si>
-    <t>CF_M08_C12, CF_M08_C13</t>
-  </si>
-  <si>
     <t>This is useful for handling complex logic or interacting with databases and other services server side from components rendered on the client without having to write an API complete It is similar to a simulation of an API, allowing a simpler integration and direct from the server logic in the application.</t>
   </si>
   <si>
@@ -137,9 +104,6 @@
   </si>
   <si>
     <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
-  </si>
-  <si>
-    <t>CF_M08_C15,</t>
   </si>
   <si>
     <t>Traefik opens port 80 to handle non-secure HTTP traffic re-
@@ -180,6 +144,42 @@
   </si>
   <si>
     <t>CF_M08_AD12</t>
+  </si>
+  <si>
+    <t>*CF_M08_C10</t>
+  </si>
+  <si>
+    <t>*CF_M08_C11, *CF_M08_C12</t>
+  </si>
+  <si>
+    <t>*CF_M08_C14</t>
+  </si>
+  <si>
+    <t>*CF_M08_C15</t>
+  </si>
+  <si>
+    <t>*CF_M08_C16</t>
+  </si>
+  <si>
+    <t>*CF_M08_C17</t>
+  </si>
+  <si>
+    <t>*CF_M08_C20, *CF_M08_C21</t>
+  </si>
+  <si>
+    <t>*CF_M08_C22</t>
+  </si>
+  <si>
+    <t>*CF_M08_C18, *CF_M08_C19</t>
+  </si>
+  <si>
+    <t>*CF_M08_C24</t>
+  </si>
+  <si>
+    <t>*CF_M08_C23</t>
+  </si>
+  <si>
+    <t>CF_M08_C08, *CF_M08_C09</t>
   </si>
 </sst>
 </file>
@@ -652,13 +652,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>7</v>
@@ -672,16 +672,16 @@
         <v>6</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F3" s="9">
         <v>43</v>
@@ -692,13 +692,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>8</v>
@@ -712,13 +712,13 @@
         <v>6</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>9</v>
@@ -732,13 +732,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>10</v>
@@ -752,13 +752,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>11</v>
@@ -772,16 +772,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F8" s="9">
         <v>46</v>
@@ -792,13 +792,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>12</v>
@@ -812,13 +812,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
@@ -832,13 +832,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>14</v>
@@ -852,16 +852,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F12" s="9">
         <v>50</v>
@@ -872,16 +872,16 @@
         <v>6</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F13" s="9">
         <v>50</v>

--- a/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
+++ b/resource/groundTruths/decision/CF_M08_ground_truth_decision.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oguzarslan/Desktop/upc/semester-4/Thesis/MappingGenerator/resource/groundTruths/decision/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4030650F-4F0D-7148-A85D-3EC4E5D41168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E3A6EF-BA24-A94E-901C-E3A2438A5C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17260" yWindow="940" windowWidth="18620" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
+    <workbookView xWindow="10780" yWindow="940" windowWidth="18620" windowHeight="16420" xr2:uid="{62E08A4D-93B2-534F-834C-F4E19BDCC923}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>Document ID</t>
   </si>
@@ -180,6 +180,30 @@
   </si>
   <si>
     <t>CF_M08_C08, *CF_M08_C09</t>
+  </si>
+  <si>
+    <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
+  </si>
+  <si>
+    <t>CF_M08_AD13</t>
+  </si>
+  <si>
+    <t>CF_M08_AD14</t>
+  </si>
+  <si>
+    <t>CF_M08_C06</t>
+  </si>
+  <si>
+    <t>CF_M08_P05</t>
+  </si>
+  <si>
+    <t>CF_M08_P03</t>
+  </si>
+  <si>
+    <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+  </si>
+  <si>
+    <t>*CF_M08_C21, CF_M08_C05</t>
   </si>
 </sst>
 </file>
@@ -618,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2D616AB-2B88-2A42-A2F9-40D380514760}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.6640625" customWidth="1"/>
@@ -887,6 +911,46 @@
         <v>50</v>
       </c>
     </row>
+    <row r="14" spans="1:6" ht="57" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="9">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="9">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
